--- a/scripts/productos-digitales/guia-pasteleria/build/calculadora-capex-pasteleria.xlsx
+++ b/scripts/productos-digitales/guia-pasteleria/build/calculadora-capex-pasteleria.xlsx
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>15562.21</v>
+        <v>15528.82</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Personal con Seguridad Social, retribución del propietario, alquiler, suministros, seguros, gestoría, amortización e intereses DEL AÑO 1 (la carga máxima, antes de que corra la carencia). Es un valor por defecto para que el fondo de maniobra tenga un número: el cálculo bueno, mes a mes -con el interés del año de crucero, más bajo-, es el libro 5 (plan-financiero-3-anos-pasteleria.xlsx). Por eso el CAPEX y el fondo de maniobra de este libro difieren en unos 134 € de los del libro 5: para citar la INVERSIÓN TOTAL, usa siempre el libro 5, no éste.</t>
+          <t>Personal con Seguridad Social, retribución del propietario, alquiler, suministros, seguros, gestoría, amortización e intereses DEL AÑO DE CRUCERO (el año 2, ya pasada la carencia). Es el mismo gasto fijo mensual que calcula, mes a mes, el libro 5 (plan-financiero-3-anos-pasteleria.xlsx), así que los dos libros publican el mismo fondo de maniobra y la misma inversión total. Si cambias este valor, cámbialo también allí.</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B19" s="10">
         <f>IFERROR(B16*B18,"")</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Batidora planetaria, 20 L — Sammic BP-20</t>
+          <t>Batidora planetaria, 20 L — Sammic BE-20</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3648,19 +3648,19 @@
       </c>
       <c r="H36" s="10">
         <f>'Parámetros'!B19</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="I36" s="10">
         <f>'Parámetros'!B19</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="J36" s="10">
         <f>'Parámetros'!B19</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="K36" s="10">
         <f>IF(D36="No","",IFERROR(IF(F36="Sí",J36/(1+G36),J36),""))</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="L36" s="10">
         <f>IF(K36="","",IFERROR(K36*G36,""))</f>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="M36" s="10">
         <f>IF(K36="","",IFERROR(K36+L36,""))</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="N39" s="15">
         <f>IFERROR(K39/$K$47,"")</f>
-        <v>0.35518654610854206</v>
+        <v>0.3553946876805953</v>
       </c>
     </row>
     <row r="40">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="N40" s="15">
         <f>IFERROR(K40/$K$47,"")</f>
-        <v>0.23809004154562058</v>
+        <v>0.23822956382223964</v>
       </c>
     </row>
     <row r="41">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="N41" s="15">
         <f>IFERROR(K41/$K$47,"")</f>
-        <v>0.055620020611053804</v>
+        <v>0.05565261429641283</v>
       </c>
     </row>
     <row r="42">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="N42" s="15">
         <f>IFERROR(K42/$K$47,"")</f>
-        <v>0.034729351175057446</v>
+        <v>0.03474970279543598</v>
       </c>
     </row>
     <row r="43">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="N43" s="15">
         <f>IFERROR(K43/$K$47,"")</f>
-        <v>0.010524045810623469</v>
+        <v>0.010530212968313935</v>
       </c>
     </row>
     <row r="44">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="N44" s="15">
         <f>IFERROR(K44/$K$47,"")</f>
-        <v>0.010962547719399446</v>
+        <v>0.010968971841993682</v>
       </c>
     </row>
     <row r="45">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="N45" s="15">
         <f>IFERROR(K45/$K$47,"")</f>
-        <v>0.02192509543879889</v>
+        <v>0.021937943683987365</v>
       </c>
     </row>
     <row r="46">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="K46" s="10">
         <f>SUMIF($B$6:$B$36,C46,K$6:K$36)</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="L46" s="10">
         <f>SUMIF($B$6:$B$36,C46,L$6:L$36)</f>
@@ -3866,11 +3866,11 @@
       </c>
       <c r="M46" s="10">
         <f>SUMIF($B$6:$B$36,C46,M$6:M$36)</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="N46" s="15">
         <f>IFERROR(K46/$K$47,"")</f>
-        <v>0.2729623515909044</v>
+        <v>0.2725363029110213</v>
       </c>
     </row>
     <row r="47">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="K47" s="16">
         <f>SUM(K39:K46)</f>
-        <v>228049.17834710743</v>
+        <v>227915.61834710743</v>
       </c>
       <c r="L47" s="16">
         <f>SUM(L39:L46)</f>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M47" s="16">
         <f>SUM(M39:M46)</f>
-        <v>261960.0494</v>
+        <v>261826.4894</v>
       </c>
     </row>
     <row r="48">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="K49" s="17">
         <f>M47</f>
-        <v>261960.0494</v>
+        <v>261826.4894</v>
       </c>
     </row>
     <row r="50"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C11" s="10">
         <f>'CAPEX por Bloque'!K46</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
     </row>
     <row r="12"/>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="J15" s="10">
         <f>IFERROR(I15+$C$11*H15,"")</f>
-        <v>228049.17834710743</v>
+        <v>227915.61834710743</v>
       </c>
       <c r="K15" s="10" t="n">
         <v>100000</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(I16+$C$11*H16,"")</f>
-        <v>27416.203752066118</v>
+        <v>27389.49175206612</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>3000</v>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(I17+$C$11*H17,"")</f>
-        <v>101709.72725619834</v>
+        <v>101642.94725619834</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>8000</v>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J18" s="10">
         <f>IFERROR(I18+$C$11*H18,"")</f>
-        <v>95297.02783471074</v>
+        <v>95216.89183471074</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>15000</v>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J19" s="10">
         <f>IFERROR(I19+$C$11*H19,"")</f>
-        <v>275430.21826446283</v>
+        <v>275269.94626446284</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>60000</v>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="J20" s="10">
         <f>IFERROR(I20+$C$11*H20,"")</f>
-        <v>129571.15950413223</v>
+        <v>129477.66750413223</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>60000</v>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="J21" s="10">
         <f>IFERROR(I21+$C$11*H21,"")</f>
-        <v>358527.74985123967</v>
+        <v>358327.40985123964</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>150000</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="J22" s="10">
         <f>IFERROR(I22+$C$11*H22,"")</f>
-        <v>245900.88234710746</v>
+        <v>245753.96634710743</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>83000</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J23" s="10">
         <f>IFERROR(I23+$C$11*H23,"")</f>
-        <v>305316.2933553719</v>
+        <v>305142.6653553719</v>
       </c>
       <c r="M23" s="15">
         <f>IF(OR(K23="",L23=""),"",IFERROR(I23/((K23+L23)/2)-1,""))</f>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="J24" s="10">
         <f>IFERROR(I24+$C$11*H24,"")</f>
-        <v>229428.8021818182</v>
+        <v>229295.2421818182</v>
       </c>
       <c r="M24" s="15">
         <f>IF(OR(K24="",L24=""),"",IFERROR(I24/((K24+L24)/2)-1,""))</f>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B13" s="10">
         <f>'CAPEX por Bloque'!K46</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="C13" s="10">
         <f>'CAPEX por Bloque'!L46</f>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="D13" s="10">
         <f>'CAPEX por Bloque'!M46</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
     </row>
     <row r="14">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="B14" s="16">
         <f>SUM(B6:B13)</f>
-        <v>228049.17834710743</v>
+        <v>227915.61834710743</v>
       </c>
       <c r="C14" s="16">
         <f>SUM(C6:C13)</f>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D14" s="16">
         <f>SUM(D6:D13)</f>
-        <v>261960.0494</v>
+        <v>261826.4894</v>
       </c>
     </row>
     <row r="15">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B21" s="10">
         <f>B14</f>
-        <v>228049.17834710743</v>
+        <v>227915.61834710743</v>
       </c>
     </row>
     <row r="22">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="B23" s="16">
         <f>D14</f>
-        <v>261960.0494</v>
+        <v>261826.4894</v>
       </c>
     </row>
     <row r="24">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B24" s="10">
         <f>'CAPEX por Bloque'!K46</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
     </row>
     <row r="25">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B26" s="16">
         <f>IFERROR(B23-B25,"")</f>
-        <v>201960.0494</v>
+        <v>201826.4894</v>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="B8" s="10">
         <f>'CAPEX por Bloque'!K47</f>
-        <v>228049.17834710743</v>
+        <v>227915.61834710743</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="B10" s="10">
         <f>'CAPEX por Bloque'!M47</f>
-        <v>261960.0494</v>
+        <v>261826.4894</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="B15" s="10">
         <f>'CAPEX por Bloque'!K46</f>
-        <v>62248.84</v>
+        <v>62115.28</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B16" s="10">
         <f>'IVA y Tesorería'!B26</f>
-        <v>201960.0494</v>
+        <v>201826.4894</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
